--- a/sheet/8617.xlsx
+++ b/sheet/8617.xlsx
@@ -914,10 +914,10 @@
         <v>9.5</v>
       </c>
       <c r="G13" t="n">
-        <v>4.07</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-5.43</v>
+        <v>0.22</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1834,10 +1834,10 @@
         <v>9.5</v>
       </c>
       <c r="G37" t="n">
-        <v>4.1</v>
+        <v>9.73</v>
       </c>
       <c r="H37" t="n">
-        <v>-5.4</v>
+        <v>0.23</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2294,10 +2294,10 @@
         <v>9.5</v>
       </c>
       <c r="G49" t="n">
-        <v>4.07</v>
+        <v>9.74</v>
       </c>
       <c r="H49" t="n">
-        <v>-5.43</v>
+        <v>0.24</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2754,10 +2754,10 @@
         <v>9.5</v>
       </c>
       <c r="G61" t="n">
-        <v>4.85</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="H61" t="n">
-        <v>-4.65</v>
+        <v>0.12</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3214,10 +3214,10 @@
         <v>9.5</v>
       </c>
       <c r="G73" t="n">
-        <v>4.07</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="H73" t="n">
-        <v>-5.43</v>
+        <v>0.14</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         <v>9.5</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>10.05</v>
       </c>
       <c r="H97" t="n">
-        <v>-9.5</v>
+        <v>0.55</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -4594,10 +4594,10 @@
         <v>9.5</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>11.52</v>
       </c>
       <c r="H109" t="n">
-        <v>-9.5</v>
+        <v>2.02</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -5514,10 +5514,10 @@
         <v>9.5</v>
       </c>
       <c r="G133" t="n">
-        <v>4.12</v>
+        <v>9.57</v>
       </c>
       <c r="H133" t="n">
-        <v>-5.38</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -5974,10 +5974,10 @@
         <v>9.5</v>
       </c>
       <c r="G145" t="n">
-        <v>4.35</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="H145" t="n">
-        <v>-5.15</v>
+        <v>0.45</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
@@ -6434,10 +6434,10 @@
         <v>9.5</v>
       </c>
       <c r="G157" t="n">
-        <v>0</v>
+        <v>9.85</v>
       </c>
       <c r="H157" t="n">
-        <v>-9.5</v>
+        <v>0.35</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -6894,10 +6894,10 @@
         <v>9.5</v>
       </c>
       <c r="G169" t="n">
-        <v>3.97</v>
+        <v>9.52</v>
       </c>
       <c r="H169" t="n">
-        <v>-5.53</v>
+        <v>0.02</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
@@ -7354,10 +7354,10 @@
         <v>9.5</v>
       </c>
       <c r="G181" t="n">
-        <v>4.05</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="H181" t="n">
-        <v>-5.45</v>
+        <v>0.05</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
@@ -7814,10 +7814,10 @@
         <v>9.5</v>
       </c>
       <c r="G193" t="n">
-        <v>4.1</v>
+        <v>9.57</v>
       </c>
       <c r="H193" t="n">
-        <v>-5.4</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
@@ -8274,10 +8274,10 @@
         <v>9.5</v>
       </c>
       <c r="G205" t="n">
-        <v>4.03</v>
+        <v>9.56</v>
       </c>
       <c r="H205" t="n">
-        <v>-5.47</v>
+        <v>0.06</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
@@ -8734,10 +8734,10 @@
         <v>9.5</v>
       </c>
       <c r="G217" t="n">
-        <v>4.08</v>
+        <v>10.73</v>
       </c>
       <c r="H217" t="n">
-        <v>-5.42</v>
+        <v>1.23</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
@@ -9654,10 +9654,10 @@
         <v>9.5</v>
       </c>
       <c r="G241" t="n">
-        <v>4.55</v>
+        <v>10.67</v>
       </c>
       <c r="H241" t="n">
-        <v>-4.95</v>
+        <v>1.17</v>
       </c>
       <c r="I241" t="inlineStr">
         <is>
@@ -10114,10 +10114,10 @@
         <v>9.5</v>
       </c>
       <c r="G253" t="n">
-        <v>4.08</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="H253" t="n">
-        <v>-5.42</v>
+        <v>0.13</v>
       </c>
       <c r="I253" t="inlineStr">
         <is>
@@ -10574,10 +10574,10 @@
         <v>9.5</v>
       </c>
       <c r="G265" t="n">
-        <v>4.15</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="H265" t="n">
-        <v>-5.35</v>
+        <v>0.28</v>
       </c>
       <c r="I265" t="inlineStr">
         <is>
@@ -11094,10 +11094,10 @@
         <v>87</v>
       </c>
       <c r="C2" t="n">
-        <v>73.34999999999999</v>
+        <v>79</v>
       </c>
       <c r="D2" t="n">
-        <v>-13.65</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="3">
@@ -11126,10 +11126,10 @@
         <v>87</v>
       </c>
       <c r="C4" t="n">
-        <v>83.06</v>
+        <v>88.69</v>
       </c>
       <c r="D4" t="n">
-        <v>-3.94</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="5">
@@ -11142,10 +11142,10 @@
         <v>87.5</v>
       </c>
       <c r="C5" t="n">
-        <v>70.77000000000001</v>
+        <v>76.44</v>
       </c>
       <c r="D5" t="n">
-        <v>-16.73</v>
+        <v>-11.06</v>
       </c>
     </row>
     <row r="6">
@@ -11158,10 +11158,10 @@
         <v>87</v>
       </c>
       <c r="C6" t="n">
-        <v>60.68</v>
+        <v>65.45</v>
       </c>
       <c r="D6" t="n">
-        <v>-26.32</v>
+        <v>-21.55</v>
       </c>
     </row>
     <row r="7">
@@ -11174,10 +11174,10 @@
         <v>87</v>
       </c>
       <c r="C7" t="n">
-        <v>76.03</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>-10.97</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="8">
@@ -11206,10 +11206,10 @@
         <v>87</v>
       </c>
       <c r="C9" t="n">
-        <v>53.89</v>
+        <v>63.94</v>
       </c>
       <c r="D9" t="n">
-        <v>-33.11</v>
+        <v>-23.06</v>
       </c>
     </row>
     <row r="10">
@@ -11222,10 +11222,10 @@
         <v>87</v>
       </c>
       <c r="C10" t="n">
-        <v>40.54</v>
+        <v>52.06</v>
       </c>
       <c r="D10" t="n">
-        <v>-46.46</v>
+        <v>-34.94</v>
       </c>
     </row>
     <row r="11">
@@ -11254,10 +11254,10 @@
         <v>87</v>
       </c>
       <c r="C12" t="n">
-        <v>74.52</v>
+        <v>79.97</v>
       </c>
       <c r="D12" t="n">
-        <v>-12.48</v>
+        <v>-7.029999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -11270,10 +11270,10 @@
         <v>87</v>
       </c>
       <c r="C13" t="n">
-        <v>70.23999999999999</v>
+        <v>75.84</v>
       </c>
       <c r="D13" t="n">
-        <v>-16.76</v>
+        <v>-11.16</v>
       </c>
     </row>
     <row r="14">
@@ -11286,10 +11286,10 @@
         <v>87</v>
       </c>
       <c r="C14" t="n">
-        <v>64.42</v>
+        <v>74.27</v>
       </c>
       <c r="D14" t="n">
-        <v>-22.58</v>
+        <v>-12.73</v>
       </c>
     </row>
     <row r="15">
@@ -11302,10 +11302,10 @@
         <v>87</v>
       </c>
       <c r="C15" t="n">
-        <v>70.18000000000001</v>
+        <v>75.73</v>
       </c>
       <c r="D15" t="n">
-        <v>-16.82</v>
+        <v>-11.27</v>
       </c>
     </row>
     <row r="16">
@@ -11318,10 +11318,10 @@
         <v>87</v>
       </c>
       <c r="C16" t="n">
-        <v>80.72</v>
+        <v>86.22</v>
       </c>
       <c r="D16" t="n">
-        <v>-6.28</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="17">
@@ -11334,10 +11334,10 @@
         <v>87.5</v>
       </c>
       <c r="C17" t="n">
-        <v>70.88</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>-16.62</v>
+        <v>-11.15</v>
       </c>
     </row>
     <row r="18">
@@ -11350,10 +11350,10 @@
         <v>87.5</v>
       </c>
       <c r="C18" t="n">
-        <v>79.31</v>
+        <v>84.84</v>
       </c>
       <c r="D18" t="n">
-        <v>-8.19</v>
+        <v>-2.66</v>
       </c>
     </row>
     <row r="19">
@@ -11366,10 +11366,10 @@
         <v>87.5</v>
       </c>
       <c r="C19" t="n">
-        <v>53.85</v>
+        <v>60.5</v>
       </c>
       <c r="D19" t="n">
-        <v>-33.65</v>
+        <v>-27</v>
       </c>
     </row>
     <row r="20">
@@ -11398,10 +11398,10 @@
         <v>87.5</v>
       </c>
       <c r="C21" t="n">
-        <v>59.92</v>
+        <v>66.03999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>-27.58</v>
+        <v>-21.46</v>
       </c>
     </row>
     <row r="22">
@@ -11414,10 +11414,10 @@
         <v>87.5</v>
       </c>
       <c r="C22" t="n">
-        <v>81.47</v>
+        <v>87.02</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.03</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="23">
@@ -11430,10 +11430,10 @@
         <v>87.5</v>
       </c>
       <c r="C23" t="n">
-        <v>83</v>
+        <v>88.63</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.5</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="24">

--- a/sheet/8617.xlsx
+++ b/sheet/8617.xlsx
@@ -1264,10 +1264,10 @@
         <v>9.5</v>
       </c>
       <c r="G22" t="n">
-        <v>4.12</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>-5.38</v>
+        <v>0.04</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2074,10 +2074,10 @@
         <v>9.5</v>
       </c>
       <c r="G43" t="n">
-        <v>4.1</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="H43" t="n">
-        <v>-5.4</v>
+        <v>-1.38</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2884,10 +2884,10 @@
         <v>9.5</v>
       </c>
       <c r="G64" t="n">
-        <v>4.57</v>
+        <v>9.6</v>
       </c>
       <c r="H64" t="n">
-        <v>-4.93</v>
+        <v>0.1</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3694,10 +3694,10 @@
         <v>9.5</v>
       </c>
       <c r="G85" t="n">
-        <v>4.05</v>
+        <v>9.65</v>
       </c>
       <c r="H85" t="n">
-        <v>-5.45</v>
+        <v>0.15</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4474,10 +4474,10 @@
         <v>9.5</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H106" t="n">
-        <v>-9.5</v>
+        <v>0.2</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -5284,10 +5284,10 @@
         <v>9.5</v>
       </c>
       <c r="G127" t="n">
-        <v>4.07</v>
+        <v>9.67</v>
       </c>
       <c r="H127" t="n">
-        <v>-5.43</v>
+        <v>0.17</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         <v>9.5</v>
       </c>
       <c r="G148" t="n">
-        <v>4.03</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="H148" t="n">
-        <v>-5.47</v>
+        <v>-0.47</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
@@ -6864,10 +6864,10 @@
         <v>9.5</v>
       </c>
       <c r="G169" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H169" t="n">
-        <v>-9.5</v>
+        <v>0.5</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
@@ -7674,10 +7674,10 @@
         <v>9.5</v>
       </c>
       <c r="G190" t="n">
-        <v>0</v>
+        <v>10.02</v>
       </c>
       <c r="H190" t="n">
-        <v>-9.5</v>
+        <v>0.52</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
@@ -8484,10 +8484,10 @@
         <v>9.5</v>
       </c>
       <c r="G211" t="n">
-        <v>0</v>
+        <v>9.02</v>
       </c>
       <c r="H211" t="n">
-        <v>-9.5</v>
+        <v>-0.48</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
@@ -9294,10 +9294,10 @@
         <v>9.5</v>
       </c>
       <c r="G232" t="n">
-        <v>4.12</v>
+        <v>9.44</v>
       </c>
       <c r="H232" t="n">
-        <v>-5.38</v>
+        <v>-0.06</v>
       </c>
       <c r="I232" t="inlineStr">
         <is>
@@ -10104,10 +10104,10 @@
         <v>9.5</v>
       </c>
       <c r="G253" t="n">
-        <v>4.33</v>
+        <v>9.31</v>
       </c>
       <c r="H253" t="n">
-        <v>-5.17</v>
+        <v>-0.19</v>
       </c>
       <c r="I253" t="inlineStr">
         <is>
@@ -10914,10 +10914,10 @@
         <v>9.5</v>
       </c>
       <c r="G274" t="n">
-        <v>0</v>
+        <v>8.85</v>
       </c>
       <c r="H274" t="n">
-        <v>-9.5</v>
+        <v>-0.65</v>
       </c>
       <c r="I274" t="inlineStr">
         <is>
@@ -11714,10 +11714,10 @@
         <v>9.5</v>
       </c>
       <c r="G295" t="n">
-        <v>4.07</v>
+        <v>9.42</v>
       </c>
       <c r="H295" t="n">
-        <v>-5.43</v>
+        <v>-0.08</v>
       </c>
       <c r="I295" t="inlineStr">
         <is>
@@ -12524,10 +12524,10 @@
         <v>9.5</v>
       </c>
       <c r="G316" t="n">
-        <v>4.03</v>
+        <v>9.56</v>
       </c>
       <c r="H316" t="n">
-        <v>-5.47</v>
+        <v>0.06</v>
       </c>
       <c r="I316" t="inlineStr">
         <is>
@@ -13334,10 +13334,10 @@
         <v>9.5</v>
       </c>
       <c r="G337" t="n">
-        <v>4.12</v>
+        <v>9.1</v>
       </c>
       <c r="H337" t="n">
-        <v>-5.38</v>
+        <v>-0.4</v>
       </c>
       <c r="I337" t="inlineStr">
         <is>
@@ -14144,10 +14144,10 @@
         <v>9.5</v>
       </c>
       <c r="G358" t="n">
-        <v>4.02</v>
+        <v>9.4</v>
       </c>
       <c r="H358" t="n">
-        <v>-5.48</v>
+        <v>-0.1</v>
       </c>
       <c r="I358" t="inlineStr">
         <is>
@@ -14954,10 +14954,10 @@
         <v>9.5</v>
       </c>
       <c r="G379" t="n">
-        <v>4.03</v>
+        <v>9.31</v>
       </c>
       <c r="H379" t="n">
-        <v>-5.47</v>
+        <v>-0.19</v>
       </c>
       <c r="I379" t="inlineStr">
         <is>
@@ -15754,10 +15754,10 @@
         <v>9.5</v>
       </c>
       <c r="G400" t="n">
-        <v>4.07</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="H400" t="n">
-        <v>-5.43</v>
+        <v>-0.95</v>
       </c>
       <c r="I400" t="inlineStr">
         <is>
@@ -16554,10 +16554,10 @@
         <v>9.5</v>
       </c>
       <c r="G421" t="n">
-        <v>3.8</v>
+        <v>10.07</v>
       </c>
       <c r="H421" t="n">
-        <v>-5.7</v>
+        <v>0.57</v>
       </c>
       <c r="I421" t="inlineStr">
         <is>
@@ -17364,10 +17364,10 @@
         <v>9.5</v>
       </c>
       <c r="G442" t="n">
-        <v>4.05</v>
+        <v>9.6</v>
       </c>
       <c r="H442" t="n">
-        <v>-5.45</v>
+        <v>0.1</v>
       </c>
       <c r="I442" t="inlineStr">
         <is>
@@ -18174,10 +18174,10 @@
         <v>9.5</v>
       </c>
       <c r="G463" t="n">
-        <v>4.08</v>
+        <v>9.73</v>
       </c>
       <c r="H463" t="n">
-        <v>-5.42</v>
+        <v>0.23</v>
       </c>
       <c r="I463" t="inlineStr">
         <is>
@@ -18984,10 +18984,10 @@
         <v>9.5</v>
       </c>
       <c r="G484" t="n">
-        <v>3.87</v>
+        <v>8.59</v>
       </c>
       <c r="H484" t="n">
-        <v>-5.63</v>
+        <v>-0.91</v>
       </c>
       <c r="I484" t="inlineStr">
         <is>
@@ -19044,10 +19044,10 @@
         <v>158.75</v>
       </c>
       <c r="C2" t="n">
-        <v>150.13</v>
+        <v>155.55</v>
       </c>
       <c r="D2" t="n">
-        <v>-8.619999999999999</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="3">
@@ -19060,10 +19060,10 @@
         <v>158.75</v>
       </c>
       <c r="C3" t="n">
-        <v>119.67</v>
+        <v>123.69</v>
       </c>
       <c r="D3" t="n">
-        <v>-39.08</v>
+        <v>-35.06</v>
       </c>
     </row>
     <row r="4">
@@ -19076,10 +19076,10 @@
         <v>158.75</v>
       </c>
       <c r="C4" t="n">
-        <v>157.44</v>
+        <v>162.47</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.31</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="5">
@@ -19092,10 +19092,10 @@
         <v>159.25</v>
       </c>
       <c r="C5" t="n">
-        <v>143.68</v>
+        <v>149.28</v>
       </c>
       <c r="D5" t="n">
-        <v>-15.57</v>
+        <v>-9.970000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -19108,10 +19108,10 @@
         <v>154.25</v>
       </c>
       <c r="C6" t="n">
-        <v>121.63</v>
+        <v>131.33</v>
       </c>
       <c r="D6" t="n">
-        <v>-32.62</v>
+        <v>-22.92</v>
       </c>
     </row>
     <row r="7">
@@ -19124,10 +19124,10 @@
         <v>158.75</v>
       </c>
       <c r="C7" t="n">
-        <v>143.19</v>
+        <v>148.79</v>
       </c>
       <c r="D7" t="n">
-        <v>-15.56</v>
+        <v>-9.960000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -19140,10 +19140,10 @@
         <v>157.25</v>
       </c>
       <c r="C8" t="n">
-        <v>144.55</v>
+        <v>149.55</v>
       </c>
       <c r="D8" t="n">
-        <v>-12.7</v>
+        <v>-7.7</v>
       </c>
     </row>
     <row r="9">
@@ -19156,10 +19156,10 @@
         <v>158</v>
       </c>
       <c r="C9" t="n">
-        <v>143.79</v>
+        <v>153.79</v>
       </c>
       <c r="D9" t="n">
-        <v>-14.21</v>
+        <v>-4.21</v>
       </c>
     </row>
     <row r="10">
@@ -19172,10 +19172,10 @@
         <v>158.75</v>
       </c>
       <c r="C10" t="n">
-        <v>113.9</v>
+        <v>123.92</v>
       </c>
       <c r="D10" t="n">
-        <v>-44.85</v>
+        <v>-34.83</v>
       </c>
     </row>
     <row r="11">
@@ -19188,10 +19188,10 @@
         <v>158.75</v>
       </c>
       <c r="C11" t="n">
-        <v>109.63</v>
+        <v>118.65</v>
       </c>
       <c r="D11" t="n">
-        <v>-49.12</v>
+        <v>-40.1</v>
       </c>
     </row>
     <row r="12">
@@ -19204,10 +19204,10 @@
         <v>158.75</v>
       </c>
       <c r="C12" t="n">
-        <v>142.38</v>
+        <v>147.7</v>
       </c>
       <c r="D12" t="n">
-        <v>-16.37</v>
+        <v>-11.05</v>
       </c>
     </row>
     <row r="13">
@@ -19220,10 +19220,10 @@
         <v>158.75</v>
       </c>
       <c r="C13" t="n">
-        <v>136.41</v>
+        <v>141.39</v>
       </c>
       <c r="D13" t="n">
-        <v>-22.34</v>
+        <v>-17.36</v>
       </c>
     </row>
     <row r="14">
@@ -19236,10 +19236,10 @@
         <v>158.75</v>
       </c>
       <c r="C14" t="n">
-        <v>114.69</v>
+        <v>123.54</v>
       </c>
       <c r="D14" t="n">
-        <v>-44.06</v>
+        <v>-35.21</v>
       </c>
     </row>
     <row r="15">
@@ -19252,10 +19252,10 @@
         <v>157.5</v>
       </c>
       <c r="C15" t="n">
-        <v>152.95</v>
+        <v>158.3</v>
       </c>
       <c r="D15" t="n">
-        <v>-4.55</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="16">
@@ -19268,10 +19268,10 @@
         <v>158.75</v>
       </c>
       <c r="C16" t="n">
-        <v>152.43</v>
+        <v>157.96</v>
       </c>
       <c r="D16" t="n">
-        <v>-6.319999999999999</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="17">
@@ -19284,10 +19284,10 @@
         <v>159.25</v>
       </c>
       <c r="C17" t="n">
-        <v>137.46</v>
+        <v>142.44</v>
       </c>
       <c r="D17" t="n">
-        <v>-21.79</v>
+        <v>-16.81</v>
       </c>
     </row>
     <row r="18">
@@ -19300,10 +19300,10 @@
         <v>159.25</v>
       </c>
       <c r="C18" t="n">
-        <v>147.75</v>
+        <v>153.13</v>
       </c>
       <c r="D18" t="n">
-        <v>-11.5</v>
+        <v>-6.12</v>
       </c>
     </row>
     <row r="19">
@@ -19316,10 +19316,10 @@
         <v>159.25</v>
       </c>
       <c r="C19" t="n">
-        <v>137.33</v>
+        <v>142.61</v>
       </c>
       <c r="D19" t="n">
-        <v>-21.92</v>
+        <v>-16.64</v>
       </c>
     </row>
     <row r="20">
@@ -19332,10 +19332,10 @@
         <v>157.75</v>
       </c>
       <c r="C20" t="n">
-        <v>123.5</v>
+        <v>127.98</v>
       </c>
       <c r="D20" t="n">
-        <v>-34.25</v>
+        <v>-29.77</v>
       </c>
     </row>
     <row r="21">
@@ -19348,10 +19348,10 @@
         <v>157.75</v>
       </c>
       <c r="C21" t="n">
-        <v>142.92</v>
+        <v>149.19</v>
       </c>
       <c r="D21" t="n">
-        <v>-14.83</v>
+        <v>-8.56</v>
       </c>
     </row>
     <row r="22">
@@ -19364,10 +19364,10 @@
         <v>159.25</v>
       </c>
       <c r="C22" t="n">
-        <v>149.09</v>
+        <v>154.64</v>
       </c>
       <c r="D22" t="n">
-        <v>-10.16</v>
+        <v>-4.61</v>
       </c>
     </row>
     <row r="23">
@@ -19380,10 +19380,10 @@
         <v>159.25</v>
       </c>
       <c r="C23" t="n">
-        <v>151.11</v>
+        <v>156.76</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.140000000000001</v>
+        <v>-2.49</v>
       </c>
     </row>
     <row r="24">
@@ -19396,10 +19396,10 @@
         <v>159.25</v>
       </c>
       <c r="C24" t="n">
-        <v>123.19</v>
+        <v>127.91</v>
       </c>
       <c r="D24" t="n">
-        <v>-36.06</v>
+        <v>-31.34</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/8617.xlsx
+++ b/sheet/8617.xlsx
@@ -1534,10 +1534,10 @@
         <v>9.5</v>
       </c>
       <c r="G29" t="n">
-        <v>4.22</v>
+        <v>9.69</v>
       </c>
       <c r="H29" t="n">
-        <v>-5.28</v>
+        <v>0.19</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2614,10 +2614,10 @@
         <v>9.5</v>
       </c>
       <c r="G57" t="n">
-        <v>4.12</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="H57" t="n">
-        <v>-5.38</v>
+        <v>-1.36</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3694,10 +3694,10 @@
         <v>9.5</v>
       </c>
       <c r="G85" t="n">
-        <v>4.63</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="H85" t="n">
-        <v>-4.87</v>
+        <v>0.05</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4774,10 +4774,10 @@
         <v>9.5</v>
       </c>
       <c r="G113" t="n">
-        <v>4.17</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H113" t="n">
-        <v>-5.33</v>
+        <v>0.2</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -5824,10 +5824,10 @@
         <v>9.5</v>
       </c>
       <c r="G141" t="n">
-        <v>4.47</v>
+        <v>8.92</v>
       </c>
       <c r="H141" t="n">
-        <v>-5.03</v>
+        <v>-0.58</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
@@ -7974,10 +7974,10 @@
         <v>9.5</v>
       </c>
       <c r="G197" t="n">
-        <v>3.98</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="H197" t="n">
-        <v>-5.52</v>
+        <v>-0.22</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
@@ -9014,10 +9014,10 @@
         <v>9.5</v>
       </c>
       <c r="G225" t="n">
-        <v>0</v>
+        <v>10.02</v>
       </c>
       <c r="H225" t="n">
-        <v>-9.5</v>
+        <v>0.52</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
@@ -11174,10 +11174,10 @@
         <v>9.5</v>
       </c>
       <c r="G281" t="n">
-        <v>0</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="H281" t="n">
-        <v>-9.5</v>
+        <v>-0.45</v>
       </c>
       <c r="I281" t="inlineStr">
         <is>
@@ -12254,10 +12254,10 @@
         <v>9.5</v>
       </c>
       <c r="G309" t="n">
-        <v>4.13</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="H309" t="n">
-        <v>-5.37</v>
+        <v>-0.55</v>
       </c>
       <c r="I309" t="inlineStr">
         <is>
@@ -13334,10 +13334,10 @@
         <v>9.5</v>
       </c>
       <c r="G337" t="n">
-        <v>4.15</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="H337" t="n">
-        <v>-5.35</v>
+        <v>-0.47</v>
       </c>
       <c r="I337" t="inlineStr">
         <is>
@@ -14414,10 +14414,10 @@
         <v>9.5</v>
       </c>
       <c r="G365" t="n">
-        <v>0</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="H365" t="n">
-        <v>-9.5</v>
+        <v>0.05</v>
       </c>
       <c r="I365" t="inlineStr">
         <is>
@@ -15474,10 +15474,10 @@
         <v>9.5</v>
       </c>
       <c r="G393" t="n">
-        <v>4</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="H393" t="n">
-        <v>-5.5</v>
+        <v>-0.03</v>
       </c>
       <c r="I393" t="inlineStr">
         <is>
@@ -16554,10 +16554,10 @@
         <v>9.5</v>
       </c>
       <c r="G421" t="n">
-        <v>4.07</v>
+        <v>9.5</v>
       </c>
       <c r="H421" t="n">
-        <v>-5.43</v>
+        <v>0</v>
       </c>
       <c r="I421" t="inlineStr">
         <is>
@@ -17634,10 +17634,10 @@
         <v>9.5</v>
       </c>
       <c r="G449" t="n">
-        <v>4.12</v>
+        <v>9.49</v>
       </c>
       <c r="H449" t="n">
-        <v>-5.38</v>
+        <v>-0.01</v>
       </c>
       <c r="I449" t="inlineStr">
         <is>
@@ -18714,10 +18714,10 @@
         <v>9.5</v>
       </c>
       <c r="G477" t="n">
-        <v>4.1</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="H477" t="n">
-        <v>-5.4</v>
+        <v>0.05</v>
       </c>
       <c r="I477" t="inlineStr">
         <is>
@@ -19794,10 +19794,10 @@
         <v>9.5</v>
       </c>
       <c r="G505" t="n">
-        <v>4.12</v>
+        <v>9.5</v>
       </c>
       <c r="H505" t="n">
-        <v>-5.38</v>
+        <v>0</v>
       </c>
       <c r="I505" t="inlineStr">
         <is>
@@ -20864,10 +20864,10 @@
         <v>9.5</v>
       </c>
       <c r="G533" t="n">
-        <v>4.08</v>
+        <v>8.58</v>
       </c>
       <c r="H533" t="n">
-        <v>-5.42</v>
+        <v>-0.92</v>
       </c>
       <c r="I533" t="inlineStr">
         <is>
@@ -23014,10 +23014,10 @@
         <v>9.5</v>
       </c>
       <c r="G589" t="n">
-        <v>4.17</v>
+        <v>9.6</v>
       </c>
       <c r="H589" t="n">
-        <v>-5.33</v>
+        <v>0.1</v>
       </c>
       <c r="I589" t="inlineStr">
         <is>
@@ -24084,10 +24084,10 @@
         <v>9.5</v>
       </c>
       <c r="G617" t="n">
-        <v>4.28</v>
+        <v>9.68</v>
       </c>
       <c r="H617" t="n">
-        <v>-5.22</v>
+        <v>0.18</v>
       </c>
       <c r="I617" t="inlineStr">
         <is>
@@ -25224,10 +25224,10 @@
         <v>211.5</v>
       </c>
       <c r="C2" t="n">
-        <v>194.03</v>
+        <v>199.5</v>
       </c>
       <c r="D2" t="n">
-        <v>-17.47</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="3">
@@ -25240,10 +25240,10 @@
         <v>211.5</v>
       </c>
       <c r="C3" t="n">
-        <v>152.34</v>
+        <v>156.36</v>
       </c>
       <c r="D3" t="n">
-        <v>-59.16</v>
+        <v>-55.14</v>
       </c>
     </row>
     <row r="4">
@@ -25256,10 +25256,10 @@
         <v>211.5</v>
       </c>
       <c r="C4" t="n">
-        <v>196.4</v>
+        <v>201.32</v>
       </c>
       <c r="D4" t="n">
-        <v>-15.1</v>
+        <v>-10.18</v>
       </c>
     </row>
     <row r="5">
@@ -25272,10 +25272,10 @@
         <v>212</v>
       </c>
       <c r="C5" t="n">
-        <v>187.69</v>
+        <v>193.22</v>
       </c>
       <c r="D5" t="n">
-        <v>-24.31</v>
+        <v>-18.78</v>
       </c>
     </row>
     <row r="6">
@@ -25288,10 +25288,10 @@
         <v>207</v>
       </c>
       <c r="C6" t="n">
-        <v>170.85</v>
+        <v>175.3</v>
       </c>
       <c r="D6" t="n">
-        <v>-36.15</v>
+        <v>-31.7</v>
       </c>
     </row>
     <row r="7">
@@ -25320,10 +25320,10 @@
         <v>210</v>
       </c>
       <c r="C8" t="n">
-        <v>186.8</v>
+        <v>192.1</v>
       </c>
       <c r="D8" t="n">
-        <v>-23.2</v>
+        <v>-17.9</v>
       </c>
     </row>
     <row r="9">
@@ -25336,10 +25336,10 @@
         <v>213.5</v>
       </c>
       <c r="C9" t="n">
-        <v>194.34</v>
+        <v>204.36</v>
       </c>
       <c r="D9" t="n">
-        <v>-19.16</v>
+        <v>-9.140000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -25368,10 +25368,10 @@
         <v>211.5</v>
       </c>
       <c r="C11" t="n">
-        <v>143.3</v>
+        <v>152.35</v>
       </c>
       <c r="D11" t="n">
-        <v>-68.2</v>
+        <v>-59.15</v>
       </c>
     </row>
     <row r="12">
@@ -25384,10 +25384,10 @@
         <v>211.5</v>
       </c>
       <c r="C12" t="n">
-        <v>185.55</v>
+        <v>190.37</v>
       </c>
       <c r="D12" t="n">
-        <v>-25.95</v>
+        <v>-21.13</v>
       </c>
     </row>
     <row r="13">
@@ -25400,10 +25400,10 @@
         <v>211.5</v>
       </c>
       <c r="C13" t="n">
-        <v>171.15</v>
+        <v>176.03</v>
       </c>
       <c r="D13" t="n">
-        <v>-40.35</v>
+        <v>-35.47</v>
       </c>
     </row>
     <row r="14">
@@ -25416,10 +25416,10 @@
         <v>211.5</v>
       </c>
       <c r="C14" t="n">
-        <v>148.17</v>
+        <v>157.72</v>
       </c>
       <c r="D14" t="n">
-        <v>-63.33</v>
+        <v>-53.78</v>
       </c>
     </row>
     <row r="15">
@@ -25432,10 +25432,10 @@
         <v>208.75</v>
       </c>
       <c r="C15" t="n">
-        <v>204.47</v>
+        <v>209.94</v>
       </c>
       <c r="D15" t="n">
-        <v>-4.28</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="16">
@@ -25448,10 +25448,10 @@
         <v>211.5</v>
       </c>
       <c r="C16" t="n">
-        <v>195.68</v>
+        <v>201.11</v>
       </c>
       <c r="D16" t="n">
-        <v>-15.82</v>
+        <v>-10.39</v>
       </c>
     </row>
     <row r="17">
@@ -25464,10 +25464,10 @@
         <v>212</v>
       </c>
       <c r="C17" t="n">
-        <v>175.14</v>
+        <v>180.51</v>
       </c>
       <c r="D17" t="n">
-        <v>-36.86</v>
+        <v>-31.49</v>
       </c>
     </row>
     <row r="18">
@@ -25480,10 +25480,10 @@
         <v>212</v>
       </c>
       <c r="C18" t="n">
-        <v>191.13</v>
+        <v>196.58</v>
       </c>
       <c r="D18" t="n">
-        <v>-20.87</v>
+        <v>-15.42</v>
       </c>
     </row>
     <row r="19">
@@ -25496,10 +25496,10 @@
         <v>212</v>
       </c>
       <c r="C19" t="n">
-        <v>165.48</v>
+        <v>170.86</v>
       </c>
       <c r="D19" t="n">
-        <v>-46.52</v>
+        <v>-41.14</v>
       </c>
     </row>
     <row r="20">
@@ -25512,10 +25512,10 @@
         <v>210.5</v>
       </c>
       <c r="C20" t="n">
-        <v>157.74</v>
+        <v>162.24</v>
       </c>
       <c r="D20" t="n">
-        <v>-52.76</v>
+        <v>-48.26</v>
       </c>
     </row>
     <row r="21">
@@ -25544,10 +25544,10 @@
         <v>212</v>
       </c>
       <c r="C22" t="n">
-        <v>192.81</v>
+        <v>198.24</v>
       </c>
       <c r="D22" t="n">
-        <v>-19.19</v>
+        <v>-13.76</v>
       </c>
     </row>
     <row r="23">
@@ -25560,10 +25560,10 @@
         <v>206.5</v>
       </c>
       <c r="C23" t="n">
-        <v>199.56</v>
+        <v>204.96</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.94</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="24">
